--- a/base_normalizada.xlsx
+++ b/base_normalizada.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29303"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{198E8FF1-3195-49DF-857B-DD008F264C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW84\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928CF376-4F68-4DEE-A7A7-D9836115DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="62">
   <si>
     <t>Nº</t>
   </si>
@@ -87,9 +92,6 @@
     <t>Freio de mão travado</t>
   </si>
   <si>
-    <t>Fechado</t>
-  </si>
-  <si>
     <t>Jocimar</t>
   </si>
   <si>
@@ -171,9 +173,6 @@
     <t>Vazamento de óleo durante carregamento; acionado ramal de emergência</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
     <t>Substituição de mangueira hidráulica</t>
   </si>
   <si>
@@ -202,6 +201,27 @@
   </si>
   <si>
     <t>Problemas no giro</t>
+  </si>
+  <si>
+    <t>Problema elétrico (solenoide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vazamento no radiador e condensadora do ar condicionado danificado </t>
+  </si>
+  <si>
+    <t>Substituição das mangueiras hidráulicas da garra</t>
+  </si>
+  <si>
+    <t>EDC-711</t>
+  </si>
+  <si>
+    <t>Teste de carga</t>
+  </si>
+  <si>
+    <t>Reparo na bomba injetora da manipuladora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principio vazamento de óleo </t>
   </si>
 </sst>
 </file>
@@ -211,7 +231,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,14 +239,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -234,6 +270,7 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -271,19 +308,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -312,10 +351,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:L21">
-  <autoFilter ref="A1:L21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L21">
-    <sortCondition ref="G1:G21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:L29">
+  <autoFilter ref="A1:L29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L20">
+    <sortCondition ref="G1:G20"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nº"/>
@@ -562,8 +601,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:L29"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
@@ -578,7 +617,7 @@
     <col min="12" max="12" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -645,11 +684,12 @@
         <v>17</v>
       </c>
       <c r="J2">
-        <f>ROUND((H2-G2)*24, 2)</f>
+        <f t="shared" ref="J2:J14" si="0">ROUND((H2-G2)*24, 2)</f>
         <v>6</v>
       </c>
-      <c r="K2" t="s">
-        <v>18</v>
+      <c r="K2" t="str">
+        <f t="shared" ref="K2:K25" si="1">IF(H2="","Aberto","Fechado")</f>
+        <v>Fechado</v>
       </c>
       <c r="L2" s="3" t="str">
         <f>IF(OR(ISBLANK(G2),ISBLANK(H2)),"",IF(H2&lt;G2,"Data inválida",
@@ -657,7 +697,7 @@
         <v>0 dias e 6 horas</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -668,13 +708,13 @@
         <v>13</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
       </c>
       <c r="G3" s="2">
         <v>45789.354166666664</v>
@@ -683,14 +723,15 @@
         <v>45790.409722222219</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3">
-        <f>ROUND((H3-G3)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>25.33</v>
       </c>
-      <c r="K3" t="s">
-        <v>18</v>
+      <c r="K3" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L3" s="3" t="str">
         <f>IF(OR(ISBLANK(G3),ISBLANK(H3)),"",IF(H3&lt;G3,"Data inválida",
@@ -698,7 +739,7 @@
         <v>1 dias e 1 horas</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -724,22 +765,23 @@
         <v>45797</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J4">
-        <f>ROUND((H4-G4)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>80.62</v>
       </c>
-      <c r="K4" t="s">
-        <v>18</v>
+      <c r="K4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L4" s="3" t="str">
-        <f t="shared" ref="L4:L21" si="0">IF(OR(ISBLANK(G4),ISBLANK(H4)),"",IF(H4&lt;G4,"Data inválida",
+        <f t="shared" ref="L4:L29" si="2">IF(OR(ISBLANK(G4),ISBLANK(H4)),"",IF(H4&lt;G4,"Data inválida",
 INT(H4-G4) &amp; " dias e " &amp; TEXT(H4-G4,"h") &amp; " horas"))</f>
         <v>3 dias e 8 horas</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -750,13 +792,13 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
         <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G5" s="2">
         <v>45797.640972222223</v>
@@ -765,21 +807,22 @@
         <v>45797.677083333336</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5">
-        <f>ROUND((H5-G5)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>0.87</v>
       </c>
-      <c r="K5" t="s">
-        <v>18</v>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0 dias e 0 horas</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -790,13 +833,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2">
         <v>45810.591666666667</v>
@@ -805,18 +848,19 @@
         <v>45811</v>
       </c>
       <c r="J6">
-        <f>ROUND((H6-G6)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>9.8000000000000007</v>
       </c>
-      <c r="K6" t="s">
-        <v>18</v>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0 dias e 9 horas</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -824,13 +868,13 @@
         <v>12</v>
       </c>
       <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>28</v>
-      </c>
-      <c r="F7" t="s">
-        <v>29</v>
       </c>
       <c r="G7" s="2">
         <v>45814.333333333336</v>
@@ -839,21 +883,22 @@
         <v>45827.363194444442</v>
       </c>
       <c r="I7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J7">
-        <f>ROUND((H7-G7)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>312.72000000000003</v>
       </c>
-      <c r="K7" t="s">
-        <v>18</v>
+      <c r="K7" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>13 dias e 0 horas</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -861,13 +906,13 @@
         <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
       </c>
       <c r="G8" s="2">
         <v>45814.333333333336</v>
@@ -876,21 +921,22 @@
         <v>45814.572916666664</v>
       </c>
       <c r="I8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8">
-        <f>ROUND((H8-G8)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>5.75</v>
       </c>
-      <c r="K8" t="s">
-        <v>18</v>
+      <c r="K8" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L8" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0 dias e 5 horas</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -898,13 +944,13 @@
         <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="2">
         <v>45824.333333333336</v>
@@ -913,21 +959,22 @@
         <v>45825.620833333334</v>
       </c>
       <c r="I9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9">
-        <f>ROUND((H9-G9)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>30.9</v>
       </c>
-      <c r="K9" t="s">
-        <v>18</v>
+      <c r="K9" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L9" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1 dias e 6 horas</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -935,13 +982,13 @@
         <v>12</v>
       </c>
       <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>37</v>
-      </c>
-      <c r="F10" t="s">
-        <v>38</v>
       </c>
       <c r="G10" s="2">
         <v>45826.375</v>
@@ -950,21 +997,22 @@
         <v>45831.375</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J10">
-        <f>ROUND((H10-G10)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>120</v>
       </c>
-      <c r="K10" t="s">
-        <v>18</v>
+      <c r="K10" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L10" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5 dias e 0 horas</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -972,13 +1020,13 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>28</v>
-      </c>
-      <c r="F11" t="s">
-        <v>29</v>
       </c>
       <c r="G11" s="2">
         <v>45828.416666666664</v>
@@ -987,21 +1035,22 @@
         <v>45829.729166666664</v>
       </c>
       <c r="I11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J11">
-        <f>ROUND((H11-G11)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>31.5</v>
       </c>
-      <c r="K11" t="s">
-        <v>18</v>
+      <c r="K11" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L11" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1 dias e 7 horas</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1009,13 +1058,13 @@
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G12" s="2">
         <v>45829.729166666664</v>
@@ -1024,21 +1073,22 @@
         <v>45831</v>
       </c>
       <c r="I12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J12">
-        <f>ROUND((H12-G12)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>30.5</v>
       </c>
-      <c r="K12" t="s">
-        <v>18</v>
+      <c r="K12" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L12" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1 dias e 6 horas</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1046,13 +1096,13 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" s="2">
         <v>45829.729166666664</v>
@@ -1061,21 +1111,22 @@
         <v>45833.416666666664</v>
       </c>
       <c r="I13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J13">
-        <f>ROUND((H13-G13)*24, 2)</f>
+        <f t="shared" si="0"/>
         <v>88.5</v>
       </c>
-      <c r="K13" t="s">
-        <v>18</v>
+      <c r="K13" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L13" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3 dias e 16 horas</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1083,36 +1134,37 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G14" s="2">
-        <v>45829.729166666664</v>
+        <v>45839</v>
       </c>
       <c r="H14" s="2">
-        <v>45833.416666666664</v>
+        <v>45841.402083333334</v>
       </c>
       <c r="I14" t="s">
         <v>43</v>
       </c>
       <c r="J14">
-        <f>ROUND((H14-G14)*24, 2)</f>
-        <v>88.5</v>
-      </c>
-      <c r="K14" t="s">
-        <v>18</v>
+        <f t="shared" si="0"/>
+        <v>57.65</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>3 dias e 16 horas</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>2 dias e 9 horas</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1120,36 +1172,31 @@
         <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G15" s="2">
-        <v>45839</v>
-      </c>
-      <c r="H15" s="2">
-        <v>45841.402083333334</v>
-      </c>
+        <v>45859.451388888891</v>
+      </c>
+      <c r="H15" s="2"/>
       <c r="I15" t="s">
         <v>44</v>
       </c>
-      <c r="J15">
-        <f>ROUND((H15-G15)*24, 2)</f>
-        <v>57.65</v>
-      </c>
-      <c r="K15" t="s">
-        <v>18</v>
+      <c r="K15" t="str">
+        <f t="shared" si="1"/>
+        <v>Aberto</v>
       </c>
       <c r="L15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>2 dias e 9 horas</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1157,30 +1204,37 @@
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G16" s="2">
-        <v>45859.451388888891</v>
-      </c>
-      <c r="H16" s="2"/>
+        <v>45881.333333333336</v>
+      </c>
+      <c r="H16" s="2">
+        <v>45895.470833333333</v>
+      </c>
       <c r="I16" t="s">
         <v>45</v>
       </c>
-      <c r="K16" t="s">
-        <v>46</v>
+      <c r="J16">
+        <f t="shared" ref="J16:J23" si="3">ROUND((H16-G16)*24, 2)</f>
+        <v>339.3</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>14 dias e 3 horas</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1188,36 +1242,37 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2">
-        <v>45881.333333333336</v>
+        <v>45881.5625</v>
       </c>
       <c r="H17" s="2">
-        <v>45895.470833333333</v>
+        <v>45883.291666666664</v>
       </c>
       <c r="I17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J17">
-        <f>ROUND((H17-G17)*24, 2)</f>
-        <v>339.3</v>
-      </c>
-      <c r="K17" t="s">
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>41.5</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>14 dias e 3 horas</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>1 dias e 17 horas</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1225,36 +1280,37 @@
         <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2">
+        <v>45884.333333333336</v>
+      </c>
+      <c r="H18" s="2">
+        <v>45887.75</v>
+      </c>
+      <c r="I18" t="s">
         <v>49</v>
       </c>
-      <c r="G18" s="2">
-        <v>45881.5625</v>
-      </c>
-      <c r="H18" s="2">
-        <v>45883.291666666664</v>
-      </c>
-      <c r="I18" t="s">
-        <v>50</v>
-      </c>
       <c r="J18">
-        <f>ROUND((H18-G18)*24, 2)</f>
-        <v>41.5</v>
-      </c>
-      <c r="K18" t="s">
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>82</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>1 dias e 17 horas</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>3 dias e 10 horas</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1262,36 +1318,37 @@
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F19" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="G19" s="2">
-        <v>45884.333333333336</v>
+        <v>45888.375</v>
       </c>
       <c r="H19" s="2">
-        <v>45887.75</v>
+        <v>45910.625</v>
       </c>
       <c r="I19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J19">
-        <f>ROUND((H19-G19)*24, 2)</f>
-        <v>82</v>
-      </c>
-      <c r="K19" t="s">
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>534</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>3 dias e 10 horas</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>22 dias e 6 horas</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1299,36 +1356,37 @@
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="2">
+        <v>45902.375</v>
+      </c>
+      <c r="H20" s="2">
+        <v>45907.291666666664</v>
+      </c>
+      <c r="I20" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="2">
-        <v>45888.375</v>
-      </c>
-      <c r="H20" s="2">
-        <v>45910.625</v>
-      </c>
-      <c r="I20" t="s">
-        <v>55</v>
-      </c>
       <c r="J20">
-        <f>ROUND((H20-G20)*24, 2)</f>
-        <v>534</v>
-      </c>
-      <c r="K20" t="s">
-        <v>18</v>
+        <f t="shared" si="3"/>
+        <v>118</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>22 dias e 6 horas</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12">
+        <f t="shared" si="2"/>
+        <v>4 dias e 22 horas</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1336,33 +1394,259 @@
         <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G21" s="2">
-        <v>45902.375</v>
+        <v>45908.432638888888</v>
       </c>
       <c r="H21" s="2">
-        <v>45907.291666666664</v>
+        <v>45916.4375</v>
       </c>
       <c r="I21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J21">
         <f>ROUND((H21-G21)*24, 2)</f>
-        <v>118</v>
-      </c>
-      <c r="K21" t="s">
-        <v>18</v>
+        <v>192.12</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
       </c>
       <c r="L21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>4 dias e 22 horas</v>
+        <f t="shared" si="2"/>
+        <v>8 dias e 0 horas</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="2">
+        <v>45924.333333333336</v>
+      </c>
+      <c r="H22" s="2">
+        <v>45945.333333333336</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>504</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
+      </c>
+      <c r="L22" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>21 dias e 0 horas</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="2">
+        <v>45884.708333333336</v>
+      </c>
+      <c r="H23" s="2">
+        <v>45940.583333333336</v>
+      </c>
+      <c r="I23" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>1341</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
+      </c>
+      <c r="L23" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>55 dias e 21 horas</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24" s="2">
+        <v>45940.3125</v>
+      </c>
+      <c r="H24" s="2">
+        <v>45944.3125</v>
+      </c>
+      <c r="I24" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24">
+        <f>ROUND((H24-G24)*24, 2)</f>
+        <v>96</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
+      </c>
+      <c r="L24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>4 dias e 0 horas</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
+      </c>
+      <c r="G25" s="2">
+        <v>45947.708333333336</v>
+      </c>
+      <c r="H25" s="2">
+        <v>45961.729166666664</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J25">
+        <f>ROUND((H25-G25)*24, 2)</f>
+        <v>336.5</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" si="1"/>
+        <v>Fechado</v>
+      </c>
+      <c r="L25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>14 dias e 0 horas</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G26" s="2">
+        <v>45962.708333333336</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ref="J26:J29" si="4">ROUND((H26-G26)*24, 2)</f>
+        <v>-1103105</v>
+      </c>
+      <c r="K26" t="str">
+        <f>IF(H26="","Aberto","Fechado")</f>
+        <v>Aberto</v>
+      </c>
+      <c r="L26" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="6"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="J27">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="J28">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="J29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1375,4 +1659,316 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010066C9F2CDDD53004FA169AAF06D8BCDB1" ma:contentTypeVersion="17" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="ab4e338aaf0ceeaf71eb2b7c98ae44da">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="078cfadf-81ba-4bd2-9020-6bf4b476ac98" xmlns:ns3="cb4a64bd-25af-446c-a7d9-624a11665c21" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bcf621d8f01fed9f18869ee314258549" ns2:_="" ns3:_="">
+    <xsd:import namespace="078cfadf-81ba-4bd2-9020-6bf4b476ac98"/>
+    <xsd:import namespace="cb4a64bd-25af-446c-a7d9-624a11665c21"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="078cfadf-81ba-4bd2-9020-6bf4b476ac98" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Compartilhado com" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Detalhes de Compartilhado Com" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{a2f4eace-fa82-45a6-aac2-07bef6fa2689}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="078cfadf-81ba-4bd2-9020-6bf4b476ac98">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb4a64bd-25af-446c-a7d9-624a11665c21" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="14" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d566a8fd-94ed-4d49-8999-3a54f140f053" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="23" nillable="true" ma:displayName="Status de liberação" ma:internalName="_x0024_Resources_x003a_core_x002c_Signoff_Status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="078cfadf-81ba-4bd2-9020-6bf4b476ac98" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{050AFD69-4D1C-46C2-B506-AA5B8655C299}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35B675CD-1EC9-4DA2-BA9F-4B0707BD1D2C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="078cfadf-81ba-4bd2-9020-6bf4b476ac98"/>
+    <ds:schemaRef ds:uri="cb4a64bd-25af-446c-a7d9-624a11665c21"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{195248A8-5A8E-4D16-9204-5EE5D7659F2B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="078cfadf-81ba-4bd2-9020-6bf4b476ac98"/>
+    <ds:schemaRef ds:uri="cb4a64bd-25af-446c-a7d9-624a11665c21"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{140b9f7d-8e3a-482f-9702-4b7ffc40985a}" enabled="1" method="Privileged" siteId="{5b6f6241-9a57-4be4-8e50-1dfa72e79a57}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>
--- a/base_normalizada.xlsx
+++ b/base_normalizada.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW84\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DW84\Downloads\manutencao_equipamentos-main-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{928CF376-4F68-4DEE-A7A7-D9836115DF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675C2D67-058F-4A60-A4EB-E155CB326A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,8 +353,8 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela1" displayName="Tabela1" ref="A1:L29">
   <autoFilter ref="A1:L29" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L20">
-    <sortCondition ref="G1:G20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L29">
+    <sortCondition ref="G1:G29"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Nº"/>
@@ -684,11 +684,11 @@
         <v>17</v>
       </c>
       <c r="J2">
-        <f t="shared" ref="J2:J14" si="0">ROUND((H2-G2)*24, 2)</f>
+        <f>ROUND((H2-G2)*24, 2)</f>
         <v>6</v>
       </c>
       <c r="K2" t="str">
-        <f t="shared" ref="K2:K25" si="1">IF(H2="","Aberto","Fechado")</f>
+        <f>IF(H2="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L2" s="3" t="str">
@@ -726,11 +726,11 @@
         <v>21</v>
       </c>
       <c r="J3">
-        <f t="shared" si="0"/>
+        <f>ROUND((H3-G3)*24, 2)</f>
         <v>25.33</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H3="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L3" s="3" t="str">
@@ -768,15 +768,15 @@
         <v>22</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
+        <f>ROUND((H4-G4)*24, 2)</f>
         <v>80.62</v>
       </c>
       <c r="K4" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H4="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L4" s="3" t="str">
-        <f t="shared" ref="L4:L29" si="2">IF(OR(ISBLANK(G4),ISBLANK(H4)),"",IF(H4&lt;G4,"Data inválida",
+        <f>IF(OR(ISBLANK(G4),ISBLANK(H4)),"",IF(H4&lt;G4,"Data inválida",
 INT(H4-G4) &amp; " dias e " &amp; TEXT(H4-G4,"h") &amp; " horas"))</f>
         <v>3 dias e 8 horas</v>
       </c>
@@ -810,15 +810,16 @@
         <v>25</v>
       </c>
       <c r="J5">
-        <f t="shared" si="0"/>
+        <f>ROUND((H5-G5)*24, 2)</f>
         <v>0.87</v>
       </c>
       <c r="K5" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H5="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G5),ISBLANK(H5)),"",IF(H5&lt;G5,"Data inválida",
+INT(H5-G5) &amp; " dias e " &amp; TEXT(H5-G5,"h") &amp; " horas"))</f>
         <v>0 dias e 0 horas</v>
       </c>
     </row>
@@ -848,15 +849,16 @@
         <v>45811</v>
       </c>
       <c r="J6">
-        <f t="shared" si="0"/>
+        <f>ROUND((H6-G6)*24, 2)</f>
         <v>9.8000000000000007</v>
       </c>
       <c r="K6" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H6="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L6" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G6),ISBLANK(H6)),"",IF(H6&lt;G6,"Data inválida",
+INT(H6-G6) &amp; " dias e " &amp; TEXT(H6-G6,"h") &amp; " horas"))</f>
         <v>0 dias e 9 horas</v>
       </c>
     </row>
@@ -886,15 +888,16 @@
         <v>29</v>
       </c>
       <c r="J7">
-        <f t="shared" si="0"/>
+        <f>ROUND((H7-G7)*24, 2)</f>
         <v>312.72000000000003</v>
       </c>
       <c r="K7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H7="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L7" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G7),ISBLANK(H7)),"",IF(H7&lt;G7,"Data inválida",
+INT(H7-G7) &amp; " dias e " &amp; TEXT(H7-G7,"h") &amp; " horas"))</f>
         <v>13 dias e 0 horas</v>
       </c>
     </row>
@@ -924,15 +927,16 @@
         <v>32</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
+        <f>ROUND((H8-G8)*24, 2)</f>
         <v>5.75</v>
       </c>
       <c r="K8" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H8="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L8" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G8),ISBLANK(H8)),"",IF(H8&lt;G8,"Data inválida",
+INT(H8-G8) &amp; " dias e " &amp; TEXT(H8-G8,"h") &amp; " horas"))</f>
         <v>0 dias e 5 horas</v>
       </c>
     </row>
@@ -962,15 +966,16 @@
         <v>34</v>
       </c>
       <c r="J9">
-        <f t="shared" si="0"/>
+        <f>ROUND((H9-G9)*24, 2)</f>
         <v>30.9</v>
       </c>
       <c r="K9" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H9="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L9" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G9),ISBLANK(H9)),"",IF(H9&lt;G9,"Data inválida",
+INT(H9-G9) &amp; " dias e " &amp; TEXT(H9-G9,"h") &amp; " horas"))</f>
         <v>1 dias e 6 horas</v>
       </c>
     </row>
@@ -1000,15 +1005,16 @@
         <v>38</v>
       </c>
       <c r="J10">
-        <f t="shared" si="0"/>
+        <f>ROUND((H10-G10)*24, 2)</f>
         <v>120</v>
       </c>
       <c r="K10" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H10="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L10" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G10),ISBLANK(H10)),"",IF(H10&lt;G10,"Data inválida",
+INT(H10-G10) &amp; " dias e " &amp; TEXT(H10-G10,"h") &amp; " horas"))</f>
         <v>5 dias e 0 horas</v>
       </c>
     </row>
@@ -1038,15 +1044,16 @@
         <v>39</v>
       </c>
       <c r="J11">
-        <f t="shared" si="0"/>
+        <f>ROUND((H11-G11)*24, 2)</f>
         <v>31.5</v>
       </c>
       <c r="K11" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H11="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L11" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G11),ISBLANK(H11)),"",IF(H11&lt;G11,"Data inválida",
+INT(H11-G11) &amp; " dias e " &amp; TEXT(H11-G11,"h") &amp; " horas"))</f>
         <v>1 dias e 7 horas</v>
       </c>
     </row>
@@ -1076,15 +1083,16 @@
         <v>41</v>
       </c>
       <c r="J12">
-        <f t="shared" si="0"/>
+        <f>ROUND((H12-G12)*24, 2)</f>
         <v>30.5</v>
       </c>
       <c r="K12" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H12="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L12" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G12),ISBLANK(H12)),"",IF(H12&lt;G12,"Data inválida",
+INT(H12-G12) &amp; " dias e " &amp; TEXT(H12-G12,"h") &amp; " horas"))</f>
         <v>1 dias e 6 horas</v>
       </c>
     </row>
@@ -1114,15 +1122,16 @@
         <v>42</v>
       </c>
       <c r="J13">
-        <f t="shared" si="0"/>
+        <f>ROUND((H13-G13)*24, 2)</f>
         <v>88.5</v>
       </c>
       <c r="K13" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H13="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L13" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G13),ISBLANK(H13)),"",IF(H13&lt;G13,"Data inválida",
+INT(H13-G13) &amp; " dias e " &amp; TEXT(H13-G13,"h") &amp; " horas"))</f>
         <v>3 dias e 16 horas</v>
       </c>
     </row>
@@ -1152,15 +1161,16 @@
         <v>43</v>
       </c>
       <c r="J14">
-        <f t="shared" si="0"/>
+        <f>ROUND((H14-G14)*24, 2)</f>
         <v>57.65</v>
       </c>
       <c r="K14" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H14="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L14" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G14),ISBLANK(H14)),"",IF(H14&lt;G14,"Data inválida",
+INT(H14-G14) &amp; " dias e " &amp; TEXT(H14-G14,"h") &amp; " horas"))</f>
         <v>2 dias e 9 horas</v>
       </c>
     </row>
@@ -1188,11 +1198,12 @@
         <v>44</v>
       </c>
       <c r="K15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H15="","Aberto","Fechado")</f>
         <v>Aberto</v>
       </c>
       <c r="L15" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G15),ISBLANK(H15)),"",IF(H15&lt;G15,"Data inválida",
+INT(H15-G15) &amp; " dias e " &amp; TEXT(H15-G15,"h") &amp; " horas"))</f>
         <v/>
       </c>
     </row>
@@ -1222,15 +1233,16 @@
         <v>45</v>
       </c>
       <c r="J16">
-        <f t="shared" ref="J16:J23" si="3">ROUND((H16-G16)*24, 2)</f>
+        <f>ROUND((H16-G16)*24, 2)</f>
         <v>339.3</v>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H16="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L16" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G16),ISBLANK(H16)),"",IF(H16&lt;G16,"Data inválida",
+INT(H16-G16) &amp; " dias e " &amp; TEXT(H16-G16,"h") &amp; " horas"))</f>
         <v>14 dias e 3 horas</v>
       </c>
     </row>
@@ -1260,15 +1272,16 @@
         <v>48</v>
       </c>
       <c r="J17">
-        <f t="shared" si="3"/>
+        <f>ROUND((H17-G17)*24, 2)</f>
         <v>41.5</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H17="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L17" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G17),ISBLANK(H17)),"",IF(H17&lt;G17,"Data inválida",
+INT(H17-G17) &amp; " dias e " &amp; TEXT(H17-G17,"h") &amp; " horas"))</f>
         <v>1 dias e 17 horas</v>
       </c>
     </row>
@@ -1298,97 +1311,100 @@
         <v>49</v>
       </c>
       <c r="J18">
-        <f t="shared" si="3"/>
+        <f>ROUND((H18-G18)*24, 2)</f>
         <v>82</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H18="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L18" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G18),ISBLANK(H18)),"",IF(H18&lt;G18,"Data inválida",
+INT(H18-G18) &amp; " dias e " &amp; TEXT(H18-G18,"h") &amp; " horas"))</f>
         <v>3 dias e 10 horas</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="G19" s="2">
-        <v>45888.375</v>
+        <v>45884.708333333336</v>
       </c>
       <c r="H19" s="2">
-        <v>45910.625</v>
+        <v>45940.583333333336</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J19">
-        <f t="shared" si="3"/>
-        <v>534</v>
+        <f>ROUND((H19-G19)*24, 2)</f>
+        <v>1341</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H19="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L19" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>22 dias e 6 horas</v>
+        <f>IF(OR(ISBLANK(G19),ISBLANK(H19)),"",IF(H19&lt;G19,"Data inválida",
+INT(H19-G19) &amp; " dias e " &amp; TEXT(H19-G19,"h") &amp; " horas"))</f>
+        <v>55 dias e 21 horas</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F20" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G20" s="2">
-        <v>45902.375</v>
+        <v>45888.375</v>
       </c>
       <c r="H20" s="2">
-        <v>45907.291666666664</v>
+        <v>45910.625</v>
       </c>
       <c r="I20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J20">
-        <f t="shared" si="3"/>
-        <v>118</v>
+        <f>ROUND((H20-G20)*24, 2)</f>
+        <v>534</v>
       </c>
       <c r="K20" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H20="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L20" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>4 dias e 22 horas</v>
+        <f>IF(OR(ISBLANK(G20),ISBLANK(H20)),"",IF(H20&lt;G20,"Data inválida",
+INT(H20-G20) &amp; " dias e " &amp; TEXT(H20-G20,"h") &amp; " horas"))</f>
+        <v>22 dias e 6 horas</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>12</v>
@@ -1403,30 +1419,31 @@
         <v>33</v>
       </c>
       <c r="G21" s="2">
-        <v>45908.432638888888</v>
+        <v>45902.375</v>
       </c>
       <c r="H21" s="2">
-        <v>45916.4375</v>
+        <v>45907.291666666664</v>
       </c>
       <c r="I21" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J21">
         <f>ROUND((H21-G21)*24, 2)</f>
-        <v>192.12</v>
+        <v>118</v>
       </c>
       <c r="K21" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H21="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L21" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>8 dias e 0 horas</v>
+        <f>IF(OR(ISBLANK(G21),ISBLANK(H21)),"",IF(H21&lt;G21,"Data inválida",
+INT(H21-G21) &amp; " dias e " &amp; TEXT(H21-G21,"h") &amp; " horas"))</f>
+        <v>4 dias e 22 horas</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
         <v>12</v>
@@ -1435,36 +1452,37 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G22" s="2">
-        <v>45924.333333333336</v>
+        <v>45908.432638888888</v>
       </c>
       <c r="H22" s="2">
-        <v>45945.333333333336</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>56</v>
+        <v>45916.4375</v>
+      </c>
+      <c r="I22" t="s">
+        <v>55</v>
       </c>
       <c r="J22">
-        <f t="shared" si="3"/>
-        <v>504</v>
+        <f>ROUND((H22-G22)*24, 2)</f>
+        <v>192.12</v>
       </c>
       <c r="K22" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H22="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L22" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>21 dias e 0 horas</v>
+        <f>IF(OR(ISBLANK(G22),ISBLANK(H22)),"",IF(H22&lt;G22,"Data inválida",
+INT(H22-G22) &amp; " dias e " &amp; TEXT(H22-G22,"h") &amp; " horas"))</f>
+        <v>8 dias e 0 horas</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -1473,31 +1491,32 @@
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F23" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G23" s="2">
-        <v>45884.708333333336</v>
+        <v>45924.333333333336</v>
       </c>
       <c r="H23" s="2">
-        <v>45940.583333333336</v>
-      </c>
-      <c r="I23" t="s">
-        <v>57</v>
+        <v>45945.333333333336</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="J23">
-        <f t="shared" si="3"/>
-        <v>1341</v>
+        <f>ROUND((H23-G23)*24, 2)</f>
+        <v>504</v>
       </c>
       <c r="K23" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H23="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L23" s="3" t="str">
-        <f t="shared" si="2"/>
-        <v>55 dias e 21 horas</v>
+        <f>IF(OR(ISBLANK(G23),ISBLANK(H23)),"",IF(H23&lt;G23,"Data inválida",
+INT(H23-G23) &amp; " dias e " &amp; TEXT(H23-G23,"h") &amp; " horas"))</f>
+        <v>21 dias e 0 horas</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1530,11 +1549,12 @@
         <v>96</v>
       </c>
       <c r="K24" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H24="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L24" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G24),ISBLANK(H24)),"",IF(H24&lt;G24,"Data inválida",
+INT(H24-G24) &amp; " dias e " &amp; TEXT(H24-G24,"h") &amp; " horas"))</f>
         <v>4 dias e 0 horas</v>
       </c>
     </row>
@@ -1568,11 +1588,12 @@
         <v>336.5</v>
       </c>
       <c r="K25" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(H25="","Aberto","Fechado")</f>
         <v>Fechado</v>
       </c>
       <c r="L25" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G25),ISBLANK(H25)),"",IF(H25&lt;G25,"Data inválida",
+INT(H25-G25) &amp; " dias e " &amp; TEXT(H25-G25,"h") &amp; " horas"))</f>
         <v>14 dias e 0 horas</v>
       </c>
     </row>
@@ -1593,22 +1614,23 @@
         <v>40</v>
       </c>
       <c r="G26" s="2">
-        <v>45962.708333333336</v>
+        <v>45965.708333333336</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" t="s">
         <v>61</v>
       </c>
       <c r="J26">
-        <f t="shared" ref="J26:J29" si="4">ROUND((H26-G26)*24, 2)</f>
-        <v>-1103105</v>
+        <f>ROUND((H26-G26)*24, 2)</f>
+        <v>-1103177</v>
       </c>
       <c r="K26" t="str">
         <f>IF(H26="","Aberto","Fechado")</f>
         <v>Aberto</v>
       </c>
       <c r="L26" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G26),ISBLANK(H26)),"",IF(H26&lt;G26,"Data inválida",
+INT(H26-G26) &amp; " dias e " &amp; TEXT(H26-G26,"h") &amp; " horas"))</f>
         <v/>
       </c>
     </row>
@@ -1617,11 +1639,12 @@
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="J27">
-        <f t="shared" si="4"/>
+        <f>ROUND((H27-G27)*24, 2)</f>
         <v>0</v>
       </c>
       <c r="L27" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G27),ISBLANK(H27)),"",IF(H27&lt;G27,"Data inválida",
+INT(H27-G27) &amp; " dias e " &amp; TEXT(H27-G27,"h") &amp; " horas"))</f>
         <v/>
       </c>
     </row>
@@ -1629,11 +1652,12 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="J28">
-        <f t="shared" si="4"/>
+        <f>ROUND((H28-G28)*24, 2)</f>
         <v>0</v>
       </c>
       <c r="L28" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G28),ISBLANK(H28)),"",IF(H28&lt;G28,"Data inválida",
+INT(H28-G28) &amp; " dias e " &amp; TEXT(H28-G28,"h") &amp; " horas"))</f>
         <v/>
       </c>
     </row>
@@ -1641,11 +1665,12 @@
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="J29">
-        <f t="shared" si="4"/>
+        <f>ROUND((H29-G29)*24, 2)</f>
         <v>0</v>
       </c>
       <c r="L29" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(OR(ISBLANK(G29),ISBLANK(H29)),"",IF(H29&lt;G29,"Data inválida",
+INT(H29-G29) &amp; " dias e " &amp; TEXT(H29-G29,"h") &amp; " horas"))</f>
         <v/>
       </c>
     </row>
@@ -1662,12 +1687,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="078cfadf-81ba-4bd2-9020-6bf4b476ac98" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1918,21 +1946,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="078cfadf-81ba-4bd2-9020-6bf4b476ac98" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb4a64bd-25af-446c-a7d9-624a11665c21">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{050AFD69-4D1C-46C2-B506-AA5B8655C299}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{195248A8-5A8E-4D16-9204-5EE5D7659F2B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="078cfadf-81ba-4bd2-9020-6bf4b476ac98"/>
+    <ds:schemaRef ds:uri="cb4a64bd-25af-446c-a7d9-624a11665c21"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1957,12 +1985,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{195248A8-5A8E-4D16-9204-5EE5D7659F2B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{050AFD69-4D1C-46C2-B506-AA5B8655C299}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="078cfadf-81ba-4bd2-9020-6bf4b476ac98"/>
-    <ds:schemaRef ds:uri="cb4a64bd-25af-446c-a7d9-624a11665c21"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
